--- a/ArduinoCode/PGN OG3D.xlsx
+++ b/ArduinoCode/PGN OG3D.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,8 +8,8 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="PGN" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="fixed IP list" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="PGN" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="fixed IP list" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,11 +21,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="124">
   <si>
     <t xml:space="preserve">Format: 0x80, 0x81, Src, PGN, Length, [Data Bytes], CRC</t>
   </si>
   <si>
+    <t xml:space="preserve">Byte 4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Name</t>
   </si>
   <si>
@@ -77,217 +80,286 @@
     <t xml:space="preserve">Byte 16</t>
   </si>
   <si>
+    <t xml:space="preserve">Byte 5 to 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 13 to 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 21 to 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNSS data1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Int64 longitude x 1 000 000 000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Int64 latitude x 1000 000 000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int32 altitude mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uint16 Dual heading x 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uint16 Single heading x 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int16 Dual roll x100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int16 km/h x 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uint16 IMU heading x 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int16 IMU roll x100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int16 IMU pitch x 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int16 IMU yaw rate x100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uint16 HDOP x 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uint16 Age x 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">byte fix quality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte sat nbr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valve data to OG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valve direction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pwmValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cutValve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BladeOffsetSlave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leverUpValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">levelSideVal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bladeOffsetIn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pwnHist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data to valve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int32 target altitude mm, &gt;20000 if none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cut valve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blade offset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">settings to valve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwmGainUp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwmGainDw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwmMinUp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwmMinDw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwmMaxUp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwmMaxDw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integal Multip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deadband</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bautrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">header hi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">header lo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USB OG out  :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relayRateData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">option1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">option2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">option3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">option4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relayRateSettings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F8</t>
+  </si>
+  <si>
     <t xml:space="preserve">autoSteerData</t>
   </si>
   <si>
-    <t xml:space="preserve">7F</t>
-  </si>
-  <si>
     <t xml:space="preserve">FE</t>
   </si>
   <si>
-    <t xml:space="preserve">Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">steerAngle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SC1to8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SC9to16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fromAutoSteer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ActualSteerAngle * 100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMU Heading Hi/Lo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMU Roll Hi/Lo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PWMDisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">steerSettings</t>
+    <t xml:space="preserve">not used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">autoSteerSettings</t>
   </si>
   <si>
     <t xml:space="preserve">FC</t>
   </si>
   <si>
-    <t xml:space="preserve">gainP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">highPWM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lowPWM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">minPWM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">countsPerDeg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">steerOffset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ackermanFix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">steerConfig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">set0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pulseCount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">minSpeed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sett1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Byte 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Byte 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Byte 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Byte 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bautrate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">header hi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">header lo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USB OG out  :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">relayRateData</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cut valve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blade offset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">option1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">option2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">option3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">option4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">relayRateSettings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwmGainUp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwmGainDw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwmMinUp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwmMinDw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwmMaxUp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwmMaxDw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integal Multip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deadband</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not used</t>
-  </si>
-  <si>
-    <t xml:space="preserve">autoSteerSettings</t>
-  </si>
-  <si>
     <t xml:space="preserve">Blade to OG3D (USB)</t>
   </si>
   <si>
-    <t xml:space="preserve">valve direction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pwmValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cutValve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BladeOffsetSlave</t>
-  </si>
-  <si>
     <t xml:space="preserve">0 or 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">leverUpValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">levelSideVal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bladeOffsetIn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pwnHist</t>
   </si>
   <si>
     <t xml:space="preserve">IP Addresses when using fixed IPs</t>
@@ -407,17 +479,17 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="8"/>
       <color rgb="FF444444"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -609,204 +681,228 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="56">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -882,24 +978,139 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18A303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369A3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A33E03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8E03A3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="C99C00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="C9211E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000EE"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551A8B"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R39"/>
-  <sheetFormatPr defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AML37"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="2" width="5.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="8.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="9.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="4" width="9.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="13.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="8" style="4" width="9.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="5" width="9.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="5" width="9.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="19" style="6" width="9.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="2" width="8.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="9.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="4" width="12.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="9.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="4" width="12.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="4" width="10.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="4" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="4" width="9.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="5" width="9.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="5" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="5" width="9.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="6" width="9.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="21" style="6" width="9.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="6" width="11.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="6" width="12.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1026" min="39" style="6" width="9.13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -912,14 +1123,21 @@
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="2" s="12" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
+      <c r="B2" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="D2" s="9"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="10"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
@@ -929,30 +1147,29 @@
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
       <c r="O2" s="10"/>
-      <c r="P2" s="11"/>
+      <c r="P2" s="10"/>
       <c r="Q2" s="11"/>
       <c r="R2" s="11"/>
-    </row>
-    <row r="3" s="21" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="S2" s="11"/>
+    </row>
+    <row r="3" s="21" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="D3" s="15"/>
+      <c r="E3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="17" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="18" t="s">
@@ -979,337 +1196,1441 @@
       <c r="O3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="19" t="s">
+      <c r="P3" s="18" t="s">
         <v>16</v>
       </c>
       <c r="Q3" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="R3" s="20"/>
+      <c r="R3" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="S3" s="20"/>
     </row>
     <row r="4" s="12" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="27"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="26"/>
       <c r="I4" s="27"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" s="26"/>
       <c r="M4" s="27"/>
       <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="11"/>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="33" t="n">
-        <f aca="false">HEX2DEC(C5)</f>
-        <v>254</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" s="34" t="s">
+      <c r="O4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34" t="s">
+      <c r="P4" s="27"/>
+      <c r="Q4" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="35" t="s">
+      <c r="R4" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="35"/>
-      <c r="K5" s="4" t="s">
+      <c r="S4" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="34" t="s">
+      <c r="T4" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="34" t="s">
+      <c r="U4" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="34" t="s">
+      <c r="V4" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="O5" s="34"/>
+      <c r="W4" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y4" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z4" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA4" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB4" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC4" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD4" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE4" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF4" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG4" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH4" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI4" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ4" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK4" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL4" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM4" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN4" s="29"/>
+      <c r="AO4" s="29"/>
+      <c r="AP4" s="29"/>
+      <c r="AQ4" s="29"/>
+      <c r="AR4" s="29"/>
+      <c r="AS4" s="29"/>
+      <c r="AT4" s="29"/>
+    </row>
+    <row r="5" s="39" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="33" t="n">
+        <v>42</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="36" t="s">
+        <v>50</v>
+      </c>
       <c r="P5" s="36"/>
+      <c r="Q5" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="R5" s="34"/>
+      <c r="S5" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="T5" s="34"/>
+      <c r="U5" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="V5" s="36"/>
+      <c r="W5" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="X5" s="36"/>
+      <c r="Y5" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z5" s="34"/>
+      <c r="AA5" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB5" s="36"/>
+      <c r="AC5" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD5" s="36"/>
+      <c r="AE5" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF5" s="36"/>
+      <c r="AG5" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="AH5" s="36"/>
+      <c r="AI5" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ5" s="36"/>
+      <c r="AK5" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL5" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="AM5" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="AN5" s="37"/>
+      <c r="AO5" s="37"/>
+      <c r="AP5" s="37"/>
+      <c r="AQ5" s="37"/>
+      <c r="AR5" s="37"/>
+      <c r="AS5" s="37"/>
+      <c r="AT5" s="37"/>
+      <c r="AU5" s="38"/>
+      <c r="AV5" s="38"/>
+      <c r="AW5" s="38"/>
+      <c r="AX5" s="38"/>
+      <c r="AY5" s="38"/>
+      <c r="AZ5" s="38"/>
+      <c r="BA5" s="38"/>
+      <c r="BB5" s="38"/>
+      <c r="BC5" s="38"/>
+      <c r="BD5" s="38"/>
+      <c r="BE5" s="38"/>
+      <c r="BF5" s="38"/>
+      <c r="BG5" s="38"/>
+      <c r="BH5" s="38"/>
+      <c r="BI5" s="38"/>
+      <c r="BJ5" s="38"/>
+      <c r="BK5" s="38"/>
+      <c r="BL5" s="38"/>
+      <c r="BM5" s="38"/>
+      <c r="BN5" s="38"/>
+      <c r="BO5" s="38"/>
+      <c r="BP5" s="38"/>
+      <c r="BQ5" s="38"/>
+      <c r="BR5" s="38"/>
+      <c r="BS5" s="38"/>
+      <c r="BT5" s="38"/>
+      <c r="BU5" s="38"/>
+      <c r="BV5" s="38"/>
+      <c r="BW5" s="38"/>
+      <c r="BX5" s="38"/>
+      <c r="BY5" s="38"/>
+      <c r="BZ5" s="38"/>
+      <c r="CA5" s="38"/>
+      <c r="CB5" s="38"/>
+      <c r="CC5" s="38"/>
+      <c r="CD5" s="38"/>
+      <c r="CE5" s="38"/>
+      <c r="CF5" s="38"/>
+      <c r="CG5" s="38"/>
+      <c r="CH5" s="38"/>
+      <c r="CI5" s="38"/>
+      <c r="CJ5" s="38"/>
+      <c r="CK5" s="38"/>
+      <c r="CL5" s="38"/>
+      <c r="CM5" s="38"/>
+      <c r="CN5" s="38"/>
+      <c r="CO5" s="38"/>
+      <c r="CP5" s="38"/>
+      <c r="CQ5" s="38"/>
+      <c r="CR5" s="38"/>
+      <c r="CS5" s="38"/>
+      <c r="CT5" s="38"/>
+      <c r="CU5" s="38"/>
+      <c r="CV5" s="38"/>
+      <c r="CW5" s="38"/>
+      <c r="CX5" s="38"/>
+      <c r="CY5" s="38"/>
+      <c r="CZ5" s="38"/>
+      <c r="DA5" s="38"/>
+      <c r="DB5" s="38"/>
+      <c r="DC5" s="38"/>
+      <c r="DD5" s="38"/>
+      <c r="DE5" s="38"/>
+      <c r="DF5" s="38"/>
+      <c r="DG5" s="38"/>
+      <c r="DH5" s="38"/>
+      <c r="DI5" s="38"/>
+      <c r="DJ5" s="38"/>
+      <c r="DK5" s="38"/>
+      <c r="DL5" s="38"/>
+      <c r="DM5" s="38"/>
+      <c r="DN5" s="38"/>
+      <c r="DO5" s="38"/>
+      <c r="DP5" s="38"/>
+      <c r="DQ5" s="38"/>
+      <c r="DR5" s="38"/>
+      <c r="DS5" s="38"/>
+      <c r="DT5" s="38"/>
+      <c r="DU5" s="38"/>
+      <c r="DV5" s="38"/>
+      <c r="DW5" s="38"/>
+      <c r="DX5" s="38"/>
+      <c r="DY5" s="38"/>
+      <c r="DZ5" s="38"/>
+      <c r="EA5" s="38"/>
+      <c r="EB5" s="38"/>
+      <c r="EC5" s="38"/>
+      <c r="ED5" s="38"/>
+      <c r="EE5" s="38"/>
+      <c r="EF5" s="38"/>
+      <c r="EG5" s="38"/>
+      <c r="EH5" s="38"/>
+      <c r="EI5" s="38"/>
+      <c r="EJ5" s="38"/>
+      <c r="EK5" s="38"/>
+      <c r="EL5" s="38"/>
+      <c r="EM5" s="38"/>
+      <c r="EN5" s="38"/>
+      <c r="EO5" s="38"/>
+      <c r="EP5" s="38"/>
+      <c r="EQ5" s="38"/>
+      <c r="ER5" s="38"/>
+      <c r="ES5" s="38"/>
+      <c r="ET5" s="38"/>
+      <c r="EU5" s="38"/>
+      <c r="EV5" s="38"/>
+      <c r="EW5" s="38"/>
+      <c r="EX5" s="38"/>
+      <c r="EY5" s="38"/>
+      <c r="EZ5" s="38"/>
+      <c r="FA5" s="38"/>
+      <c r="FB5" s="38"/>
+      <c r="FC5" s="38"/>
+      <c r="FD5" s="38"/>
+      <c r="FE5" s="38"/>
+      <c r="FF5" s="38"/>
+      <c r="FG5" s="38"/>
+      <c r="FH5" s="38"/>
+      <c r="FI5" s="38"/>
+      <c r="FJ5" s="38"/>
+      <c r="FK5" s="38"/>
+      <c r="FL5" s="38"/>
+      <c r="FM5" s="38"/>
+      <c r="FN5" s="38"/>
+      <c r="FO5" s="38"/>
+      <c r="FP5" s="38"/>
+      <c r="FQ5" s="38"/>
+      <c r="FR5" s="38"/>
+      <c r="FS5" s="38"/>
+      <c r="FT5" s="38"/>
+      <c r="FU5" s="38"/>
+      <c r="FV5" s="38"/>
+      <c r="FW5" s="38"/>
+      <c r="FX5" s="38"/>
+      <c r="FY5" s="38"/>
+      <c r="FZ5" s="38"/>
+      <c r="GA5" s="38"/>
+      <c r="GB5" s="38"/>
+      <c r="GC5" s="38"/>
+      <c r="GD5" s="38"/>
+      <c r="GE5" s="38"/>
+      <c r="GF5" s="38"/>
+      <c r="GG5" s="38"/>
+      <c r="GH5" s="38"/>
+      <c r="GI5" s="38"/>
+      <c r="GJ5" s="38"/>
+      <c r="GK5" s="38"/>
+      <c r="GL5" s="38"/>
+      <c r="GM5" s="38"/>
+      <c r="GN5" s="38"/>
+      <c r="GO5" s="38"/>
+      <c r="GP5" s="38"/>
+      <c r="GQ5" s="38"/>
+      <c r="GR5" s="38"/>
+      <c r="GS5" s="38"/>
+      <c r="GT5" s="38"/>
+      <c r="GU5" s="38"/>
+      <c r="GV5" s="38"/>
+      <c r="GW5" s="38"/>
+      <c r="GX5" s="38"/>
+      <c r="GY5" s="38"/>
+      <c r="GZ5" s="38"/>
+      <c r="HA5" s="38"/>
+      <c r="HB5" s="38"/>
+      <c r="HC5" s="38"/>
+      <c r="HD5" s="38"/>
+      <c r="HE5" s="38"/>
+      <c r="HF5" s="38"/>
+      <c r="HG5" s="38"/>
+      <c r="HH5" s="38"/>
+      <c r="HI5" s="38"/>
+      <c r="HJ5" s="38"/>
+      <c r="HK5" s="38"/>
+      <c r="HL5" s="38"/>
+      <c r="HM5" s="38"/>
+      <c r="HN5" s="38"/>
+      <c r="HO5" s="38"/>
+      <c r="HP5" s="38"/>
+      <c r="HQ5" s="38"/>
+      <c r="HR5" s="38"/>
+      <c r="HS5" s="38"/>
+      <c r="HT5" s="38"/>
+      <c r="HU5" s="38"/>
+      <c r="HV5" s="38"/>
+      <c r="HW5" s="38"/>
+      <c r="HX5" s="38"/>
+      <c r="HY5" s="38"/>
+      <c r="HZ5" s="38"/>
+      <c r="IA5" s="38"/>
+      <c r="IB5" s="38"/>
+      <c r="IC5" s="38"/>
+      <c r="ID5" s="38"/>
+      <c r="IE5" s="38"/>
+      <c r="IF5" s="38"/>
+      <c r="IG5" s="38"/>
+      <c r="IH5" s="38"/>
+      <c r="II5" s="38"/>
+      <c r="IJ5" s="38"/>
+      <c r="IK5" s="38"/>
+      <c r="IL5" s="38"/>
+      <c r="IM5" s="38"/>
+      <c r="IN5" s="38"/>
+      <c r="IO5" s="38"/>
+      <c r="IP5" s="38"/>
+      <c r="IQ5" s="38"/>
+      <c r="IR5" s="38"/>
+      <c r="IS5" s="38"/>
+      <c r="IT5" s="38"/>
+      <c r="IU5" s="38"/>
+      <c r="IV5" s="38"/>
+      <c r="IW5" s="38"/>
+      <c r="IX5" s="38"/>
+      <c r="IY5" s="38"/>
+      <c r="IZ5" s="38"/>
+      <c r="JA5" s="38"/>
+      <c r="JB5" s="38"/>
+      <c r="JC5" s="38"/>
+      <c r="JD5" s="38"/>
+      <c r="JE5" s="38"/>
+      <c r="JF5" s="38"/>
+      <c r="JG5" s="38"/>
+      <c r="JH5" s="38"/>
+      <c r="JI5" s="38"/>
+      <c r="JJ5" s="38"/>
+      <c r="JK5" s="38"/>
+      <c r="JL5" s="38"/>
+      <c r="JM5" s="38"/>
+      <c r="JN5" s="38"/>
+      <c r="JO5" s="38"/>
+      <c r="JP5" s="38"/>
+      <c r="JQ5" s="38"/>
+      <c r="JR5" s="38"/>
+      <c r="JS5" s="38"/>
+      <c r="JT5" s="38"/>
+      <c r="JU5" s="38"/>
+      <c r="JV5" s="38"/>
+      <c r="JW5" s="38"/>
+      <c r="JX5" s="38"/>
+      <c r="JY5" s="38"/>
+      <c r="JZ5" s="38"/>
+      <c r="KA5" s="38"/>
+      <c r="KB5" s="38"/>
+      <c r="KC5" s="38"/>
+      <c r="KD5" s="38"/>
+      <c r="KE5" s="38"/>
+      <c r="KF5" s="38"/>
+      <c r="KG5" s="38"/>
+      <c r="KH5" s="38"/>
+      <c r="KI5" s="38"/>
+      <c r="KJ5" s="38"/>
+      <c r="KK5" s="38"/>
+      <c r="KL5" s="38"/>
+      <c r="KM5" s="38"/>
+      <c r="KN5" s="38"/>
+      <c r="KO5" s="38"/>
+      <c r="KP5" s="38"/>
+      <c r="KQ5" s="38"/>
+      <c r="KR5" s="38"/>
+      <c r="KS5" s="38"/>
+      <c r="KT5" s="38"/>
+      <c r="KU5" s="38"/>
+      <c r="KV5" s="38"/>
+      <c r="KW5" s="38"/>
+      <c r="KX5" s="38"/>
+      <c r="KY5" s="38"/>
+      <c r="KZ5" s="38"/>
+      <c r="LA5" s="38"/>
+      <c r="LB5" s="38"/>
+      <c r="LC5" s="38"/>
+      <c r="LD5" s="38"/>
+      <c r="LE5" s="38"/>
+      <c r="LF5" s="38"/>
+      <c r="LG5" s="38"/>
+      <c r="LH5" s="38"/>
+      <c r="LI5" s="38"/>
+      <c r="LJ5" s="38"/>
+      <c r="LK5" s="38"/>
+      <c r="LL5" s="38"/>
+      <c r="LM5" s="38"/>
+      <c r="LN5" s="38"/>
+      <c r="LO5" s="38"/>
+      <c r="LP5" s="38"/>
+      <c r="LQ5" s="38"/>
+      <c r="LR5" s="38"/>
+      <c r="LS5" s="38"/>
+      <c r="LT5" s="38"/>
+      <c r="LU5" s="38"/>
+      <c r="LV5" s="38"/>
+      <c r="LW5" s="38"/>
+      <c r="LX5" s="38"/>
+      <c r="LY5" s="38"/>
+      <c r="LZ5" s="38"/>
+      <c r="MA5" s="38"/>
+      <c r="MB5" s="38"/>
+      <c r="MC5" s="38"/>
+      <c r="MD5" s="38"/>
+      <c r="ME5" s="38"/>
+      <c r="MF5" s="38"/>
+      <c r="MG5" s="38"/>
+      <c r="MH5" s="38"/>
+      <c r="MI5" s="38"/>
+      <c r="MJ5" s="38"/>
+      <c r="MK5" s="38"/>
+      <c r="ML5" s="38"/>
+      <c r="MM5" s="38"/>
+      <c r="MN5" s="38"/>
+      <c r="MO5" s="38"/>
+      <c r="MP5" s="38"/>
+      <c r="MQ5" s="38"/>
+      <c r="MR5" s="38"/>
+      <c r="MS5" s="38"/>
+      <c r="MT5" s="38"/>
+      <c r="MU5" s="38"/>
+      <c r="MV5" s="38"/>
+      <c r="MW5" s="38"/>
+      <c r="MX5" s="38"/>
+      <c r="MY5" s="38"/>
+      <c r="MZ5" s="38"/>
+      <c r="NA5" s="38"/>
+      <c r="NB5" s="38"/>
+      <c r="NC5" s="38"/>
+      <c r="ND5" s="38"/>
+      <c r="NE5" s="38"/>
+      <c r="NF5" s="38"/>
+      <c r="NG5" s="38"/>
+      <c r="NH5" s="38"/>
+      <c r="NI5" s="38"/>
+      <c r="NJ5" s="38"/>
+      <c r="NK5" s="38"/>
+      <c r="NL5" s="38"/>
+      <c r="NM5" s="38"/>
+      <c r="NN5" s="38"/>
+      <c r="NO5" s="38"/>
+      <c r="NP5" s="38"/>
+      <c r="NQ5" s="38"/>
+      <c r="NR5" s="38"/>
+      <c r="NS5" s="38"/>
+      <c r="NT5" s="38"/>
+      <c r="NU5" s="38"/>
+      <c r="NV5" s="38"/>
+      <c r="NW5" s="38"/>
+      <c r="NX5" s="38"/>
+      <c r="NY5" s="38"/>
+      <c r="NZ5" s="38"/>
+      <c r="OA5" s="38"/>
+      <c r="OB5" s="38"/>
+      <c r="OC5" s="38"/>
+      <c r="OD5" s="38"/>
+      <c r="OE5" s="38"/>
+      <c r="OF5" s="38"/>
+      <c r="OG5" s="38"/>
+      <c r="OH5" s="38"/>
+      <c r="OI5" s="38"/>
+      <c r="OJ5" s="38"/>
+      <c r="OK5" s="38"/>
+      <c r="OL5" s="38"/>
+      <c r="OM5" s="38"/>
+      <c r="ON5" s="38"/>
+      <c r="OO5" s="38"/>
+      <c r="OP5" s="38"/>
+      <c r="OQ5" s="38"/>
+      <c r="OR5" s="38"/>
+      <c r="OS5" s="38"/>
+      <c r="OT5" s="38"/>
+      <c r="OU5" s="38"/>
+      <c r="OV5" s="38"/>
+      <c r="OW5" s="38"/>
+      <c r="OX5" s="38"/>
+      <c r="OY5" s="38"/>
+      <c r="OZ5" s="38"/>
+      <c r="PA5" s="38"/>
+      <c r="PB5" s="38"/>
+      <c r="PC5" s="38"/>
+      <c r="PD5" s="38"/>
+      <c r="PE5" s="38"/>
+      <c r="PF5" s="38"/>
+      <c r="PG5" s="38"/>
+      <c r="PH5" s="38"/>
+      <c r="PI5" s="38"/>
+      <c r="PJ5" s="38"/>
+      <c r="PK5" s="38"/>
+      <c r="PL5" s="38"/>
+      <c r="PM5" s="38"/>
+      <c r="PN5" s="38"/>
+      <c r="PO5" s="38"/>
+      <c r="PP5" s="38"/>
+      <c r="PQ5" s="38"/>
+      <c r="PR5" s="38"/>
+      <c r="PS5" s="38"/>
+      <c r="PT5" s="38"/>
+      <c r="PU5" s="38"/>
+      <c r="PV5" s="38"/>
+      <c r="PW5" s="38"/>
+      <c r="PX5" s="38"/>
+      <c r="PY5" s="38"/>
+      <c r="PZ5" s="38"/>
+      <c r="QA5" s="38"/>
+      <c r="QB5" s="38"/>
+      <c r="QC5" s="38"/>
+      <c r="QD5" s="38"/>
+      <c r="QE5" s="38"/>
+      <c r="QF5" s="38"/>
+      <c r="QG5" s="38"/>
+      <c r="QH5" s="38"/>
+      <c r="QI5" s="38"/>
+      <c r="QJ5" s="38"/>
+      <c r="QK5" s="38"/>
+      <c r="QL5" s="38"/>
+      <c r="QM5" s="38"/>
+      <c r="QN5" s="38"/>
+      <c r="QO5" s="38"/>
+      <c r="QP5" s="38"/>
+      <c r="QQ5" s="38"/>
+      <c r="QR5" s="38"/>
+      <c r="QS5" s="38"/>
+      <c r="QT5" s="38"/>
+      <c r="QU5" s="38"/>
+      <c r="QV5" s="38"/>
+      <c r="QW5" s="38"/>
+      <c r="QX5" s="38"/>
+      <c r="QY5" s="38"/>
+      <c r="QZ5" s="38"/>
+      <c r="RA5" s="38"/>
+      <c r="RB5" s="38"/>
+      <c r="RC5" s="38"/>
+      <c r="RD5" s="38"/>
+      <c r="RE5" s="38"/>
+      <c r="RF5" s="38"/>
+      <c r="RG5" s="38"/>
+      <c r="RH5" s="38"/>
+      <c r="RI5" s="38"/>
+      <c r="RJ5" s="38"/>
+      <c r="RK5" s="38"/>
+      <c r="RL5" s="38"/>
+      <c r="RM5" s="38"/>
+      <c r="RN5" s="38"/>
+      <c r="RO5" s="38"/>
+      <c r="RP5" s="38"/>
+      <c r="RQ5" s="38"/>
+      <c r="RR5" s="38"/>
+      <c r="RS5" s="38"/>
+      <c r="RT5" s="38"/>
+      <c r="RU5" s="38"/>
+      <c r="RV5" s="38"/>
+      <c r="RW5" s="38"/>
+      <c r="RX5" s="38"/>
+      <c r="RY5" s="38"/>
+      <c r="RZ5" s="38"/>
+      <c r="SA5" s="38"/>
+      <c r="SB5" s="38"/>
+      <c r="SC5" s="38"/>
+      <c r="SD5" s="38"/>
+      <c r="SE5" s="38"/>
+      <c r="SF5" s="38"/>
+      <c r="SG5" s="38"/>
+      <c r="SH5" s="38"/>
+      <c r="SI5" s="38"/>
+      <c r="SJ5" s="38"/>
+      <c r="SK5" s="38"/>
+      <c r="SL5" s="38"/>
+      <c r="SM5" s="38"/>
+      <c r="SN5" s="38"/>
+      <c r="SO5" s="38"/>
+      <c r="SP5" s="38"/>
+      <c r="SQ5" s="38"/>
+      <c r="SR5" s="38"/>
+      <c r="SS5" s="38"/>
+      <c r="ST5" s="38"/>
+      <c r="SU5" s="38"/>
+      <c r="SV5" s="38"/>
+      <c r="SW5" s="38"/>
+      <c r="SX5" s="38"/>
+      <c r="SY5" s="38"/>
+      <c r="SZ5" s="38"/>
+      <c r="TA5" s="38"/>
+      <c r="TB5" s="38"/>
+      <c r="TC5" s="38"/>
+      <c r="TD5" s="38"/>
+      <c r="TE5" s="38"/>
+      <c r="TF5" s="38"/>
+      <c r="TG5" s="38"/>
+      <c r="TH5" s="38"/>
+      <c r="TI5" s="38"/>
+      <c r="TJ5" s="38"/>
+      <c r="TK5" s="38"/>
+      <c r="TL5" s="38"/>
+      <c r="TM5" s="38"/>
+      <c r="TN5" s="38"/>
+      <c r="TO5" s="38"/>
+      <c r="TP5" s="38"/>
+      <c r="TQ5" s="38"/>
+      <c r="TR5" s="38"/>
+      <c r="TS5" s="38"/>
+      <c r="TT5" s="38"/>
+      <c r="TU5" s="38"/>
+      <c r="TV5" s="38"/>
+      <c r="TW5" s="38"/>
+      <c r="TX5" s="38"/>
+      <c r="TY5" s="38"/>
+      <c r="TZ5" s="38"/>
+      <c r="UA5" s="38"/>
+      <c r="UB5" s="38"/>
+      <c r="UC5" s="38"/>
+      <c r="UD5" s="38"/>
+      <c r="UE5" s="38"/>
+      <c r="UF5" s="38"/>
+      <c r="UG5" s="38"/>
+      <c r="UH5" s="38"/>
+      <c r="UI5" s="38"/>
+      <c r="UJ5" s="38"/>
+      <c r="UK5" s="38"/>
+      <c r="UL5" s="38"/>
+      <c r="UM5" s="38"/>
+      <c r="UN5" s="38"/>
+      <c r="UO5" s="38"/>
+      <c r="UP5" s="38"/>
+      <c r="UQ5" s="38"/>
+      <c r="UR5" s="38"/>
+      <c r="US5" s="38"/>
+      <c r="UT5" s="38"/>
+      <c r="UU5" s="38"/>
+      <c r="UV5" s="38"/>
+      <c r="UW5" s="38"/>
+      <c r="UX5" s="38"/>
+      <c r="UY5" s="38"/>
+      <c r="UZ5" s="38"/>
+      <c r="VA5" s="38"/>
+      <c r="VB5" s="38"/>
+      <c r="VC5" s="38"/>
+      <c r="VD5" s="38"/>
+      <c r="VE5" s="38"/>
+      <c r="VF5" s="38"/>
+      <c r="VG5" s="38"/>
+      <c r="VH5" s="38"/>
+      <c r="VI5" s="38"/>
+      <c r="VJ5" s="38"/>
+      <c r="VK5" s="38"/>
+      <c r="VL5" s="38"/>
+      <c r="VM5" s="38"/>
+      <c r="VN5" s="38"/>
+      <c r="VO5" s="38"/>
+      <c r="VP5" s="38"/>
+      <c r="VQ5" s="38"/>
+      <c r="VR5" s="38"/>
+      <c r="VS5" s="38"/>
+      <c r="VT5" s="38"/>
+      <c r="VU5" s="38"/>
+      <c r="VV5" s="38"/>
+      <c r="VW5" s="38"/>
+      <c r="VX5" s="38"/>
+      <c r="VY5" s="38"/>
+      <c r="VZ5" s="38"/>
+      <c r="WA5" s="38"/>
+      <c r="WB5" s="38"/>
+      <c r="WC5" s="38"/>
+      <c r="WD5" s="38"/>
+      <c r="WE5" s="38"/>
+      <c r="WF5" s="38"/>
+      <c r="WG5" s="38"/>
+      <c r="WH5" s="38"/>
+      <c r="WI5" s="38"/>
+      <c r="WJ5" s="38"/>
+      <c r="WK5" s="38"/>
+      <c r="WL5" s="38"/>
+      <c r="WM5" s="38"/>
+      <c r="WN5" s="38"/>
+      <c r="WO5" s="38"/>
+      <c r="WP5" s="38"/>
+      <c r="WQ5" s="38"/>
+      <c r="WR5" s="38"/>
+      <c r="WS5" s="38"/>
+      <c r="WT5" s="38"/>
+      <c r="WU5" s="38"/>
+      <c r="WV5" s="38"/>
+      <c r="WW5" s="38"/>
+      <c r="WX5" s="38"/>
+      <c r="WY5" s="38"/>
+      <c r="WZ5" s="38"/>
+      <c r="XA5" s="38"/>
+      <c r="XB5" s="38"/>
+      <c r="XC5" s="38"/>
+      <c r="XD5" s="38"/>
+      <c r="XE5" s="38"/>
+      <c r="XF5" s="38"/>
+      <c r="XG5" s="38"/>
+      <c r="XH5" s="38"/>
+      <c r="XI5" s="38"/>
+      <c r="XJ5" s="38"/>
+      <c r="XK5" s="38"/>
+      <c r="XL5" s="38"/>
+      <c r="XM5" s="38"/>
+      <c r="XN5" s="38"/>
+      <c r="XO5" s="38"/>
+      <c r="XP5" s="38"/>
+      <c r="XQ5" s="38"/>
+      <c r="XR5" s="38"/>
+      <c r="XS5" s="38"/>
+      <c r="XT5" s="38"/>
+      <c r="XU5" s="38"/>
+      <c r="XV5" s="38"/>
+      <c r="XW5" s="38"/>
+      <c r="XX5" s="38"/>
+      <c r="XY5" s="38"/>
+      <c r="XZ5" s="38"/>
+      <c r="YA5" s="38"/>
+      <c r="YB5" s="38"/>
+      <c r="YC5" s="38"/>
+      <c r="YD5" s="38"/>
+      <c r="YE5" s="38"/>
+      <c r="YF5" s="38"/>
+      <c r="YG5" s="38"/>
+      <c r="YH5" s="38"/>
+      <c r="YI5" s="38"/>
+      <c r="YJ5" s="38"/>
+      <c r="YK5" s="38"/>
+      <c r="YL5" s="38"/>
+      <c r="YM5" s="38"/>
+      <c r="YN5" s="38"/>
+      <c r="YO5" s="38"/>
+      <c r="YP5" s="38"/>
+      <c r="YQ5" s="38"/>
+      <c r="YR5" s="38"/>
+      <c r="YS5" s="38"/>
+      <c r="YT5" s="38"/>
+      <c r="YU5" s="38"/>
+      <c r="YV5" s="38"/>
+      <c r="YW5" s="38"/>
+      <c r="YX5" s="38"/>
+      <c r="YY5" s="38"/>
+      <c r="YZ5" s="38"/>
+      <c r="ZA5" s="38"/>
+      <c r="ZB5" s="38"/>
+      <c r="ZC5" s="38"/>
+      <c r="ZD5" s="38"/>
+      <c r="ZE5" s="38"/>
+      <c r="ZF5" s="38"/>
+      <c r="ZG5" s="38"/>
+      <c r="ZH5" s="38"/>
+      <c r="ZI5" s="38"/>
+      <c r="ZJ5" s="38"/>
+      <c r="ZK5" s="38"/>
+      <c r="ZL5" s="38"/>
+      <c r="ZM5" s="38"/>
+      <c r="ZN5" s="38"/>
+      <c r="ZO5" s="38"/>
+      <c r="ZP5" s="38"/>
+      <c r="ZQ5" s="38"/>
+      <c r="ZR5" s="38"/>
+      <c r="ZS5" s="38"/>
+      <c r="ZT5" s="38"/>
+      <c r="ZU5" s="38"/>
+      <c r="ZV5" s="38"/>
+      <c r="ZW5" s="38"/>
+      <c r="ZX5" s="38"/>
+      <c r="ZY5" s="38"/>
+      <c r="ZZ5" s="38"/>
+      <c r="AAA5" s="38"/>
+      <c r="AAB5" s="38"/>
+      <c r="AAC5" s="38"/>
+      <c r="AAD5" s="38"/>
+      <c r="AAE5" s="38"/>
+      <c r="AAF5" s="38"/>
+      <c r="AAG5" s="38"/>
+      <c r="AAH5" s="38"/>
+      <c r="AAI5" s="38"/>
+      <c r="AAJ5" s="38"/>
+      <c r="AAK5" s="38"/>
+      <c r="AAL5" s="38"/>
+      <c r="AAM5" s="38"/>
+      <c r="AAN5" s="38"/>
+      <c r="AAO5" s="38"/>
+      <c r="AAP5" s="38"/>
+      <c r="AAQ5" s="38"/>
+      <c r="AAR5" s="38"/>
+      <c r="AAS5" s="38"/>
+      <c r="AAT5" s="38"/>
+      <c r="AAU5" s="38"/>
+      <c r="AAV5" s="38"/>
+      <c r="AAW5" s="38"/>
+      <c r="AAX5" s="38"/>
+      <c r="AAY5" s="38"/>
+      <c r="AAZ5" s="38"/>
+      <c r="ABA5" s="38"/>
+      <c r="ABB5" s="38"/>
+      <c r="ABC5" s="38"/>
+      <c r="ABD5" s="38"/>
+      <c r="ABE5" s="38"/>
+      <c r="ABF5" s="38"/>
+      <c r="ABG5" s="38"/>
+      <c r="ABH5" s="38"/>
+      <c r="ABI5" s="38"/>
+      <c r="ABJ5" s="38"/>
+      <c r="ABK5" s="38"/>
+      <c r="ABL5" s="38"/>
+      <c r="ABM5" s="38"/>
+      <c r="ABN5" s="38"/>
+      <c r="ABO5" s="38"/>
+      <c r="ABP5" s="38"/>
+      <c r="ABQ5" s="38"/>
+      <c r="ABR5" s="38"/>
+      <c r="ABS5" s="38"/>
+      <c r="ABT5" s="38"/>
+      <c r="ABU5" s="38"/>
+      <c r="ABV5" s="38"/>
+      <c r="ABW5" s="38"/>
+      <c r="ABX5" s="38"/>
+      <c r="ABY5" s="38"/>
+      <c r="ABZ5" s="38"/>
+      <c r="ACA5" s="38"/>
+      <c r="ACB5" s="38"/>
+      <c r="ACC5" s="38"/>
+      <c r="ACD5" s="38"/>
+      <c r="ACE5" s="38"/>
+      <c r="ACF5" s="38"/>
+      <c r="ACG5" s="38"/>
+      <c r="ACH5" s="38"/>
+      <c r="ACI5" s="38"/>
+      <c r="ACJ5" s="38"/>
+      <c r="ACK5" s="38"/>
+      <c r="ACL5" s="38"/>
+      <c r="ACM5" s="38"/>
+      <c r="ACN5" s="38"/>
+      <c r="ACO5" s="38"/>
+      <c r="ACP5" s="38"/>
+      <c r="ACQ5" s="38"/>
+      <c r="ACR5" s="38"/>
+      <c r="ACS5" s="38"/>
+      <c r="ACT5" s="38"/>
+      <c r="ACU5" s="38"/>
+      <c r="ACV5" s="38"/>
+      <c r="ACW5" s="38"/>
+      <c r="ACX5" s="38"/>
+      <c r="ACY5" s="38"/>
+      <c r="ACZ5" s="38"/>
+      <c r="ADA5" s="38"/>
+      <c r="ADB5" s="38"/>
+      <c r="ADC5" s="38"/>
+      <c r="ADD5" s="38"/>
+      <c r="ADE5" s="38"/>
+      <c r="ADF5" s="38"/>
+      <c r="ADG5" s="38"/>
+      <c r="ADH5" s="38"/>
+      <c r="ADI5" s="38"/>
+      <c r="ADJ5" s="38"/>
+      <c r="ADK5" s="38"/>
+      <c r="ADL5" s="38"/>
+      <c r="ADM5" s="38"/>
+      <c r="ADN5" s="38"/>
+      <c r="ADO5" s="38"/>
+      <c r="ADP5" s="38"/>
+      <c r="ADQ5" s="38"/>
+      <c r="ADR5" s="38"/>
+      <c r="ADS5" s="38"/>
+      <c r="ADT5" s="38"/>
+      <c r="ADU5" s="38"/>
+      <c r="ADV5" s="38"/>
+      <c r="ADW5" s="38"/>
+      <c r="ADX5" s="38"/>
+      <c r="ADY5" s="38"/>
+      <c r="ADZ5" s="38"/>
+      <c r="AEA5" s="38"/>
+      <c r="AEB5" s="38"/>
+      <c r="AEC5" s="38"/>
+      <c r="AED5" s="38"/>
+      <c r="AEE5" s="38"/>
+      <c r="AEF5" s="38"/>
+      <c r="AEG5" s="38"/>
+      <c r="AEH5" s="38"/>
+      <c r="AEI5" s="38"/>
+      <c r="AEJ5" s="38"/>
+      <c r="AEK5" s="38"/>
+      <c r="AEL5" s="38"/>
+      <c r="AEM5" s="38"/>
+      <c r="AEN5" s="38"/>
+      <c r="AEO5" s="38"/>
+      <c r="AEP5" s="38"/>
+      <c r="AEQ5" s="38"/>
+      <c r="AER5" s="38"/>
+      <c r="AES5" s="38"/>
+      <c r="AET5" s="38"/>
+      <c r="AEU5" s="38"/>
+      <c r="AEV5" s="38"/>
+      <c r="AEW5" s="38"/>
+      <c r="AEX5" s="38"/>
+      <c r="AEY5" s="38"/>
+      <c r="AEZ5" s="38"/>
+      <c r="AFA5" s="38"/>
+      <c r="AFB5" s="38"/>
+      <c r="AFC5" s="38"/>
+      <c r="AFD5" s="38"/>
+      <c r="AFE5" s="38"/>
+      <c r="AFF5" s="38"/>
+      <c r="AFG5" s="38"/>
+      <c r="AFH5" s="38"/>
+      <c r="AFI5" s="38"/>
+      <c r="AFJ5" s="38"/>
+      <c r="AFK5" s="38"/>
+      <c r="AFL5" s="38"/>
+      <c r="AFM5" s="38"/>
+      <c r="AFN5" s="38"/>
+      <c r="AFO5" s="38"/>
+      <c r="AFP5" s="38"/>
+      <c r="AFQ5" s="38"/>
+      <c r="AFR5" s="38"/>
+      <c r="AFS5" s="38"/>
+      <c r="AFT5" s="38"/>
+      <c r="AFU5" s="38"/>
+      <c r="AFV5" s="38"/>
+      <c r="AFW5" s="38"/>
+      <c r="AFX5" s="38"/>
+      <c r="AFY5" s="38"/>
+      <c r="AFZ5" s="38"/>
+      <c r="AGA5" s="38"/>
+      <c r="AGB5" s="38"/>
+      <c r="AGC5" s="38"/>
+      <c r="AGD5" s="38"/>
+      <c r="AGE5" s="38"/>
+      <c r="AGF5" s="38"/>
+      <c r="AGG5" s="38"/>
+      <c r="AGH5" s="38"/>
+      <c r="AGI5" s="38"/>
+      <c r="AGJ5" s="38"/>
+      <c r="AGK5" s="38"/>
+      <c r="AGL5" s="38"/>
+      <c r="AGM5" s="38"/>
+      <c r="AGN5" s="38"/>
+      <c r="AGO5" s="38"/>
+      <c r="AGP5" s="38"/>
+      <c r="AGQ5" s="38"/>
+      <c r="AGR5" s="38"/>
+      <c r="AGS5" s="38"/>
+      <c r="AGT5" s="38"/>
+      <c r="AGU5" s="38"/>
+      <c r="AGV5" s="38"/>
+      <c r="AGW5" s="38"/>
+      <c r="AGX5" s="38"/>
+      <c r="AGY5" s="38"/>
+      <c r="AGZ5" s="38"/>
+      <c r="AHA5" s="38"/>
+      <c r="AHB5" s="38"/>
+      <c r="AHC5" s="38"/>
+      <c r="AHD5" s="38"/>
+      <c r="AHE5" s="38"/>
+      <c r="AHF5" s="38"/>
+      <c r="AHG5" s="38"/>
+      <c r="AHH5" s="38"/>
+      <c r="AHI5" s="38"/>
+      <c r="AHJ5" s="38"/>
+      <c r="AHK5" s="38"/>
+      <c r="AHL5" s="38"/>
+      <c r="AHM5" s="38"/>
+      <c r="AHN5" s="38"/>
+      <c r="AHO5" s="38"/>
+      <c r="AHP5" s="38"/>
+      <c r="AHQ5" s="38"/>
+      <c r="AHR5" s="38"/>
+      <c r="AHS5" s="38"/>
+      <c r="AHT5" s="38"/>
+      <c r="AHU5" s="38"/>
+      <c r="AHV5" s="38"/>
+      <c r="AHW5" s="38"/>
+      <c r="AHX5" s="38"/>
+      <c r="AHY5" s="38"/>
+      <c r="AHZ5" s="38"/>
+      <c r="AIA5" s="38"/>
+      <c r="AIB5" s="38"/>
+      <c r="AIC5" s="38"/>
+      <c r="AID5" s="38"/>
+      <c r="AIE5" s="38"/>
+      <c r="AIF5" s="38"/>
+      <c r="AIG5" s="38"/>
+      <c r="AIH5" s="38"/>
+      <c r="AII5" s="38"/>
+      <c r="AIJ5" s="38"/>
+      <c r="AIK5" s="38"/>
+      <c r="AIL5" s="38"/>
+      <c r="AIM5" s="38"/>
+      <c r="AIN5" s="38"/>
+      <c r="AIO5" s="38"/>
+      <c r="AIP5" s="38"/>
+      <c r="AIQ5" s="38"/>
+      <c r="AIR5" s="38"/>
+      <c r="AIS5" s="38"/>
+      <c r="AIT5" s="38"/>
+      <c r="AIU5" s="38"/>
+      <c r="AIV5" s="38"/>
+      <c r="AIW5" s="38"/>
+      <c r="AIX5" s="38"/>
+      <c r="AIY5" s="38"/>
+      <c r="AIZ5" s="38"/>
+      <c r="AJA5" s="38"/>
+      <c r="AJB5" s="38"/>
+      <c r="AJC5" s="38"/>
+      <c r="AJD5" s="38"/>
+      <c r="AJE5" s="38"/>
+      <c r="AJF5" s="38"/>
+      <c r="AJG5" s="38"/>
+      <c r="AJH5" s="38"/>
+      <c r="AJI5" s="38"/>
+      <c r="AJJ5" s="38"/>
+      <c r="AJK5" s="38"/>
+      <c r="AJL5" s="38"/>
+      <c r="AJM5" s="38"/>
+      <c r="AJN5" s="38"/>
+      <c r="AJO5" s="38"/>
+      <c r="AJP5" s="38"/>
+      <c r="AJQ5" s="38"/>
+      <c r="AJR5" s="38"/>
+      <c r="AJS5" s="38"/>
+      <c r="AJT5" s="38"/>
+      <c r="AJU5" s="38"/>
+      <c r="AJV5" s="38"/>
+      <c r="AJW5" s="38"/>
+      <c r="AJX5" s="38"/>
+      <c r="AJY5" s="38"/>
+      <c r="AJZ5" s="38"/>
+      <c r="AKA5" s="38"/>
+      <c r="AKB5" s="38"/>
+      <c r="AKC5" s="38"/>
+      <c r="AKD5" s="38"/>
+      <c r="AKE5" s="38"/>
+      <c r="AKF5" s="38"/>
+      <c r="AKG5" s="38"/>
+      <c r="AKH5" s="38"/>
+      <c r="AKI5" s="38"/>
+      <c r="AKJ5" s="38"/>
+      <c r="AKK5" s="38"/>
+      <c r="AKL5" s="38"/>
+      <c r="AKM5" s="38"/>
+      <c r="AKN5" s="38"/>
+      <c r="AKO5" s="38"/>
+      <c r="AKP5" s="38"/>
+      <c r="AKQ5" s="38"/>
+      <c r="AKR5" s="38"/>
+      <c r="AKS5" s="38"/>
+      <c r="AKT5" s="38"/>
+      <c r="AKU5" s="38"/>
+      <c r="AKV5" s="38"/>
+      <c r="AKW5" s="38"/>
+      <c r="AKX5" s="38"/>
+      <c r="AKY5" s="38"/>
+      <c r="AKZ5" s="38"/>
+      <c r="ALA5" s="38"/>
+      <c r="ALB5" s="38"/>
+      <c r="ALC5" s="38"/>
+      <c r="ALD5" s="38"/>
+      <c r="ALE5" s="38"/>
+      <c r="ALF5" s="38"/>
+      <c r="ALG5" s="38"/>
+      <c r="ALH5" s="38"/>
+      <c r="ALI5" s="38"/>
+      <c r="ALJ5" s="38"/>
+      <c r="ALK5" s="38"/>
+      <c r="ALL5" s="38"/>
+      <c r="ALM5" s="38"/>
+      <c r="ALN5" s="38"/>
+      <c r="ALO5" s="38"/>
+      <c r="ALP5" s="38"/>
+      <c r="ALQ5" s="38"/>
+      <c r="ALR5" s="38"/>
+      <c r="ALS5" s="38"/>
+      <c r="ALT5" s="38"/>
+      <c r="ALU5" s="38"/>
+      <c r="ALV5" s="38"/>
+      <c r="ALW5" s="38"/>
+      <c r="ALX5" s="38"/>
+      <c r="ALY5" s="38"/>
+      <c r="ALZ5" s="38"/>
+      <c r="AMA5" s="38"/>
+      <c r="AMB5" s="38"/>
+      <c r="AMC5" s="38"/>
+      <c r="AMD5" s="38"/>
+      <c r="AME5" s="38"/>
+      <c r="AMF5" s="38"/>
+      <c r="AMG5" s="38"/>
+      <c r="AMH5" s="38"/>
+      <c r="AMI5" s="38"/>
+      <c r="AMJ5" s="38"/>
+      <c r="AMK5" s="38"/>
+      <c r="AML5" s="38"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <f aca="false">HEX2DEC(C7)</f>
-        <v>253</v>
-      </c>
-      <c r="E7" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="F7" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="F7" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="37"/>
-      <c r="H7" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="38"/>
-      <c r="L7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>27</v>
+      <c r="G7" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="J7" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="M7" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="N7" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>74</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>61</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <f aca="false">HEX2DEC(C9)</f>
-        <v>252</v>
-      </c>
-      <c r="E9" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="G9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K9" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="L9" s="38"/>
-      <c r="M9" s="4" t="s">
-        <v>44</v>
+        <v>76</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L9" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="M9" s="40" t="s">
+        <v>79</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>27</v>
+        <v>79</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>19</v>
+        <v>80</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>61</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <f aca="false">HEX2DEC(C11)</f>
-        <v>251</v>
-      </c>
-      <c r="E11" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="F11" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="G11" s="4" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" s="44" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="39"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="42"/>
-      <c r="L13" s="42"/>
-      <c r="M13" s="42"/>
-      <c r="N13" s="42"/>
-      <c r="O13" s="42"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="I16" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" s="47" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="42"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="45"/>
+      <c r="M13" s="45"/>
+      <c r="N13" s="45"/>
+      <c r="O13" s="45"/>
+      <c r="P13" s="45"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="46"/>
+      <c r="S13" s="46"/>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J14" s="48"/>
+      <c r="M14" s="48"/>
+      <c r="N14" s="48"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E16" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="J16" s="17" t="s">
+      <c r="J16" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="K16" s="18" t="s">
+      <c r="K16" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="L16" s="17" t="s">
+      <c r="L16" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="M16" s="18" t="s">
+      <c r="M16" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="N16" s="17" t="s">
+      <c r="N16" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="O16" s="18" t="s">
+      <c r="O16" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="P16" s="17" t="s">
+      <c r="P16" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="Q16" s="18" t="s">
+      <c r="Q16" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="R16" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R16" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S16" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E17" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="E19" s="2" t="n">
         <v>127</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>61</v>
-      </c>
       <c r="G19" s="4" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E20" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F20" s="3" t="n">
         <v>32762</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>100</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>0</v>
@@ -1320,242 +2641,248 @@
       <c r="K20" s="4" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L20" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="S21" s="5" t="n">
+        <v>38400</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F22" s="3" t="n">
+        <v>32760</v>
+      </c>
+      <c r="P22" s="6"/>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>254</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>252</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" s="47" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="G26" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>248</v>
-      </c>
-      <c r="F21" s="4" t="s">
+      <c r="H26" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="R21" s="5" t="n">
-        <v>38400</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E22" s="3" t="n">
-        <v>32760</v>
-      </c>
-      <c r="O22" s="6"/>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>254</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>252</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="26" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="B26" s="40"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="E26" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="F26" s="42" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="H26" s="42" t="s">
-        <v>63</v>
-      </c>
-      <c r="I26" s="42" t="s">
-        <v>64</v>
-      </c>
-      <c r="J26" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="K26" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="L26" s="42"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="42"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-    </row>
-    <row r="27" s="47" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="45"/>
+      <c r="I26" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="J26" s="45" t="s">
+        <v>101</v>
+      </c>
+      <c r="K26" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="L26" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="45"/>
+      <c r="P26" s="45"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="46"/>
+    </row>
+    <row r="27" s="51" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="49"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
-      <c r="D27" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="I27" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="J27" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="K27" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="L27" s="38"/>
-      <c r="M27" s="38"/>
-      <c r="N27" s="38"/>
-      <c r="O27" s="38"/>
-      <c r="P27" s="46"/>
-      <c r="Q27" s="46"/>
-      <c r="R27" s="46"/>
-    </row>
-    <row r="28" s="47" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="45"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="J27" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="K27" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="L27" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="M27" s="40"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="50"/>
+      <c r="R27" s="50"/>
+      <c r="S27" s="50"/>
+    </row>
+    <row r="28" s="51" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="49"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
-      <c r="O28" s="38"/>
-      <c r="P28" s="46"/>
-      <c r="Q28" s="46"/>
-      <c r="R28" s="46"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E31" s="7"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
-      <c r="J31" s="38"/>
-      <c r="K31" s="38"/>
-    </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F35" s="38"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
-      <c r="I35" s="38"/>
-      <c r="J35" s="38"/>
-      <c r="K35" s="38"/>
-      <c r="L35" s="38"/>
-      <c r="M35" s="38"/>
-    </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="37"/>
-      <c r="J37" s="38"/>
-      <c r="K37" s="38"/>
-      <c r="L37" s="38"/>
-      <c r="M37" s="38"/>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="40"/>
+      <c r="M28" s="40"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="40"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="50"/>
+      <c r="R28" s="50"/>
+      <c r="S28" s="50"/>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F31" s="7"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="40"/>
+      <c r="K31" s="40"/>
+      <c r="L31" s="40"/>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="40"/>
+      <c r="L35" s="40"/>
+      <c r="M35" s="40"/>
+      <c r="N35" s="40"/>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="52"/>
+      <c r="J37" s="52"/>
+      <c r="K37" s="40"/>
+      <c r="L37" s="40"/>
+      <c r="M37" s="40"/>
+      <c r="N37" s="40"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="F35:M35"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="J37:M37"/>
+  <mergeCells count="22">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="AA5:AB5"/>
+    <mergeCell ref="AC5:AD5"/>
+    <mergeCell ref="AE5:AF5"/>
+    <mergeCell ref="AG5:AH5"/>
+    <mergeCell ref="AI5:AJ5"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="G35:N35"/>
+    <mergeCell ref="G37:J37"/>
+    <mergeCell ref="K37:N37"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -1564,161 +2891,161 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="3" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="53" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="53" width="17.71"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="3" style="53" width="8.67"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="48" t="s">
-        <v>89</v>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="54" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="49" t="s">
-        <v>90</v>
+      <c r="A2" s="55" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>91</v>
+      <c r="A4" s="53" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>92</v>
+      <c r="B5" s="53" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="53" t="n">
         <v>71</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>94</v>
+      <c r="B7" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="53" t="n">
         <v>72</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>95</v>
+      <c r="B8" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="53" t="n">
         <v>73</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="53" t="n">
         <v>74</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="53" t="n">
         <v>75</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>94</v>
+      <c r="B11" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="53" t="n">
         <v>76</v>
       </c>
-      <c r="B12" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>95</v>
+      <c r="B12" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="53" t="n">
         <v>77</v>
       </c>
-      <c r="B13" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>94</v>
+      <c r="B13" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="53" t="n">
         <v>78</v>
       </c>
-      <c r="B14" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>95</v>
+      <c r="B14" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="53" t="n">
         <v>79</v>
       </c>
-      <c r="B15" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>94</v>
+      <c r="B15" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="53" t="n">
         <v>80</v>
       </c>
-      <c r="B16" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>95</v>
+      <c r="B16" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="53" t="n">
         <v>81</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="53" t="n">
         <v>82</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="53" t="n">
         <v>100</v>
       </c>
-      <c r="B22" s="0" t="s">
-        <v>99</v>
+      <c r="B22" s="53" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/ArduinoCode/PGN OG3D.xlsx
+++ b/ArduinoCode/PGN OG3D.xlsx
@@ -846,7 +846,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2429,9 +2429,12 @@
       <c r="F9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="40" t="s">
         <v>76</v>
       </c>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
       <c r="K9" s="4" t="s">
         <v>77</v>
       </c>

--- a/ArduinoCode/PGN OG3D.xlsx
+++ b/ArduinoCode/PGN OG3D.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="131">
   <si>
     <t xml:space="preserve">Format: 0x80, 0x81, Src, PGN, Length, [Data Bytes], CRC</t>
   </si>
@@ -221,145 +221,166 @@
     <t xml:space="preserve">E1</t>
   </si>
   <si>
+    <t xml:space="preserve">multipleStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pwmValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cutValve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BladeOffsetSlave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leverUpValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">levelSideVal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pwmHist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">multiple bit:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0=up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1=down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2=ready</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3=active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data to valve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int32 target altitude mm, &gt;20000 if none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cut valve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blade offset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">settings to valve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwmGainUp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwmGainDw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwmMinUp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwmMinDw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwmMaxUp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwmMaxDw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integal Multip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deadband</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bautrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">header hi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">header lo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USB OG out  :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relayRateData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">option1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">option2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">option3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">option4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relayRateSettings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">autoSteerData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">autoSteerSettings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blade to OG3D (USB)</t>
+  </si>
+  <si>
     <t xml:space="preserve">valve direction</t>
   </si>
   <si>
-    <t xml:space="preserve">pwmValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cutValve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BladeOffsetSlave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">leverUpValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">levelSideVal</t>
+    <t xml:space="preserve">0 or 1</t>
   </si>
   <si>
     <t xml:space="preserve">bladeOffsetIn</t>
   </si>
   <si>
     <t xml:space="preserve">pwnHist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data to valve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">int32 target altitude mm, &gt;20000 if none</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cut valve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blade offset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">settings to valve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwmGainUp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwmGainDw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwmMinUp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwmMinDw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwmMaxUp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwmMaxDw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integal Multip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deadband</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Byte 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Byte 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Byte 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bautrate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">header hi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">header lo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USB OG out  :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">relayRateData</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">option1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">option2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">option3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">option4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">relayRateSettings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">autoSteerData</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not used</t>
-  </si>
-  <si>
-    <t xml:space="preserve">autoSteerSettings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blade to OG3D (USB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 or 1</t>
   </si>
   <si>
     <t xml:space="preserve">IP Addresses when using fixed IPs</t>
@@ -2415,37 +2436,52 @@
       <c r="O7" s="4" t="s">
         <v>63</v>
       </c>
+      <c r="Q7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="S7" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="T7" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="U7" s="6" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>61</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G9" s="40" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H9" s="40"/>
       <c r="I9" s="40"/>
       <c r="J9" s="40"/>
       <c r="K9" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="L9" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="M9" s="40" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="O9" s="4" t="s">
         <v>63</v>
@@ -2465,40 +2501,40 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>61</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="O11" s="4" t="s">
         <v>63</v>
@@ -2532,13 +2568,13 @@
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E16" s="17" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H16" s="18" t="s">
         <v>1</v>
@@ -2574,31 +2610,31 @@
         <v>16</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E17" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>127</v>
@@ -2607,22 +2643,22 @@
         <v>250</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2650,13 +2686,13 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>127</v>
@@ -2665,28 +2701,28 @@
         <v>248</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="S21" s="5" t="n">
         <v>38400</v>
@@ -2700,13 +2736,13 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>127</v>
@@ -2715,18 +2751,18 @@
         <v>254</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>127</v>
@@ -2735,18 +2771,18 @@
         <v>252</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" s="47" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="42" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B26" s="43"/>
       <c r="C26" s="43"/>
       <c r="D26" s="43"/>
       <c r="E26" s="43" t="s">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="F26" s="44" t="s">
         <v>67</v>
@@ -2758,16 +2794,16 @@
         <v>69</v>
       </c>
       <c r="I26" s="45" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J26" s="45" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="K26" s="45" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="L26" s="45" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="M26" s="45"/>
       <c r="N26" s="45"/>
@@ -2783,7 +2819,7 @@
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="40"/>
@@ -2795,10 +2831,10 @@
         <v>71</v>
       </c>
       <c r="K27" s="40" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="L27" s="40" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="M27" s="40"/>
       <c r="N27" s="40"/>
@@ -2908,17 +2944,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="54" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="55" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="53" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2926,7 +2962,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2934,10 +2970,10 @@
         <v>71</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C7" s="53" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2945,10 +2981,10 @@
         <v>72</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C8" s="53" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2966,10 +3002,10 @@
         <v>75</v>
       </c>
       <c r="B11" s="53" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C11" s="53" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2977,10 +3013,10 @@
         <v>76</v>
       </c>
       <c r="B12" s="53" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C12" s="53" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2988,10 +3024,10 @@
         <v>77</v>
       </c>
       <c r="B13" s="53" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C13" s="53" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2999,10 +3035,10 @@
         <v>78</v>
       </c>
       <c r="B14" s="53" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C14" s="53" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3010,10 +3046,10 @@
         <v>79</v>
       </c>
       <c r="B15" s="53" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C15" s="53" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3021,10 +3057,10 @@
         <v>80</v>
       </c>
       <c r="B16" s="53" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C16" s="53" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3042,7 +3078,7 @@
         <v>100</v>
       </c>
       <c r="B22" s="53" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
